--- a/docs/Growth-v2-CBA.xlsx
+++ b/docs/Growth-v2-CBA.xlsx
@@ -33,7 +33,7 @@
     <numFmt numFmtId="170" formatCode="\₱#,##0.00;&quot;(₱&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="171" formatCode="0&quot; mo&quot;"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -178,6 +178,10 @@
     <font>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -242,7 +246,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -656,6 +660,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -909,7 +914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="69" min="1" max="1"/>
@@ -1155,6 +1160,34 @@
       <c r="B28" s="76" t="inlineStr">
         <is>
           <t>Build effort is a top-down planning estimate. docs/BRD_V2.md carries a bottom-up worksheet for IT; their figure is the authoritative one.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="141" t="inlineStr">
+        <is>
+          <t>SCOPE OF THIS WORKBOOK — read before quoting a ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Costed at 1,113 people (the 637-person pilot plus 476 in mass operations) at P61 = US$1. The three-year cost of P2,049,953 is the headline figure and matches the deck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>The BENEFIT side here counts non-mass participants only, so the base BCR of 3.5 is the CONSERVATIVE case — the deck's "mass-ops benefit excluded" row. The headline BCR of 3.8 adds 54 mass-operations participants at an assumed P260,000 loaded salary; see docs/v2-cba-model.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Four of the five run lines are bought in dollars and rise as the peso weakens. The P1,785,500 build is peso labour: it moves with neither the exchange rate nor the population.</t>
         </is>
       </c>
     </row>
@@ -1211,7 +1244,7 @@
         </is>
       </c>
       <c r="B5" s="82" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C5" s="83" t="inlineStr">
         <is>
@@ -1220,7 +1253,7 @@
       </c>
       <c r="D5" s="84" t="inlineStr">
         <is>
-          <t>Verify before circulating. A 10% move shifts every peso figure by 10%.</t>
+          <t>As of 8 September 2026. Four of the five run lines are bought in dollars, so a weaker peso RAISES the peso cost of running this. The build is peso labour and does not move.</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1264,7 @@
         </is>
       </c>
       <c r="B6" s="85" t="n">
-        <v>637</v>
+        <v>1113</v>
       </c>
       <c r="C6" s="83" t="inlineStr">
         <is>
@@ -1240,7 +1273,7 @@
       </c>
       <c r="D6" s="84" t="inlineStr">
         <is>
-          <t>Employees in scope for release 1.</t>
+          <t>The 637-person pilot in IT, Operations and HR, plus 476 in mass operations joining in wave two.</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1395,7 @@
     <row r="15" ht="15" customHeight="1" s="70">
       <c r="A15" s="81" t="inlineStr">
         <is>
-          <t>PCD analyst</t>
+          <t>HR analyst</t>
         </is>
       </c>
       <c r="B15" s="90" t="n">
@@ -1546,7 +1579,7 @@
         </is>
       </c>
       <c r="B28" s="90" t="n">
-        <v>22065</v>
+        <v>40544</v>
       </c>
       <c r="C28" s="83" t="inlineStr">
         <is>
@@ -1555,7 +1588,7 @@
       </c>
       <c r="D28" s="84" t="inlineStr">
         <is>
-          <t>7,686 scoring pairs/month at 1,500 in / 250 out tokens, Batch API at 50% of list. See docs/v2-costing-model.py.</t>
+          <t>US$380/yr at 637 people, scaled by headcount and converted at the rate above. 7,686 scoring pairs/month at 1,500 in / 250 out tokens, Batch API at 50% of list.</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1599,7 @@
         </is>
       </c>
       <c r="B29" s="90" t="n">
-        <v>8700</v>
+        <v>15987</v>
       </c>
       <c r="C29" s="83" t="inlineStr">
         <is>
@@ -1575,7 +1608,7 @@
       </c>
       <c r="D29" s="84" t="inlineStr">
         <is>
-          <t>Includes the "did you apply?" nudge — the cheapest line here and the one that converts a click into a countable application.</t>
+          <t>US$150/yr at 637 people, scaled by headcount. Includes the "did you apply?" nudge — the cheapest line here and the one that converts a click into a countable application.</t>
         </is>
       </c>
     </row>
@@ -1586,11 +1619,16 @@
         </is>
       </c>
       <c r="B30" s="90" t="n">
-        <v>6960</v>
+        <v>7320</v>
       </c>
       <c r="C30" s="83" t="inlineStr">
         <is>
           <t>₱ / year</t>
+        </is>
+      </c>
+      <c r="D30" s="69" t="inlineStr">
+        <is>
+          <t>US$120/yr, converted at the rate above.</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1639,7 @@
         </is>
       </c>
       <c r="B31" s="92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C31" s="83" t="inlineStr">
         <is>
@@ -1610,7 +1648,7 @@
       </c>
       <c r="D31" s="84" t="inlineStr">
         <is>
-          <t>Quarterly, not monthly. Year 2 onward — year 1 has no referral engine to reconcile.</t>
+          <t>Quarterly, not monthly, and up from 4 hours with the larger population. Year 2 onward — year 1 has no referral engine to reconcile.</t>
         </is>
       </c>
     </row>
@@ -1730,7 +1768,7 @@
       </c>
       <c r="D39" s="84" t="inlineStr">
         <is>
-          <t>19% of the population. Scales the retention benefit linearly.</t>
+          <t>Non-mass participants only, 19% of the 637. This workbook therefore reproduces the CONSERVATIVE case in the deck — mass-operations retention benefit excluded, BCR 3.5. docs/v2-cba-model.py adds 54 mass-ops participants at a P260,000 loaded salary for the headline BCR 3.8.</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1893,7 @@
       </c>
       <c r="D49" s="84" t="inlineStr">
         <is>
-          <t>At 637 seats the binding constraint is the vendor minimum contract value, not the per-seat rate.</t>
+          <t>At 1,113 seats the binding constraint is the vendor minimum contract value, not the per-seat rate.</t>
         </is>
       </c>
     </row>
@@ -3336,7 +3374,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="23.85" customHeight="1" s="70">
       <c r="A4" s="97" t="inlineStr">
         <is>
@@ -6504,7 +6541,6 @@
         <v/>
       </c>
     </row>
-    <row r="41"/>
     <row r="42" ht="15" customHeight="1" s="70">
       <c r="A42" s="75" t="inlineStr">
         <is>

--- a/docs/Growth-v2-CBA.xlsx
+++ b/docs/Growth-v2-CBA.xlsx
@@ -931,7 +931,7 @@
     <row r="2" ht="15" customHeight="1" s="70">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Home Credit PH · 637 employees · 3-year horizon · prepared 31 August 2026</t>
+          <t>Home Credit PH · 1,113 employees · 3-year horizon · prepared 31 August 2026 · benefit side revised 11 September 2026</t>
         </is>
       </c>
     </row>
@@ -1135,7 +1135,7 @@
       </c>
       <c r="B26" s="76" t="inlineStr">
         <is>
-          <t>The retention lift is a judgement, not a measurement. The v1 dashboard shows 94% retention among participants against 81% company-wide; that 13-point gap is almost certainly selection bias, so it is discounted to 3 points here. The CBA sheet reports the case with this stream removed entirely, because it is the softest input in the model.</t>
+          <t>The retention lift is a judgement, not a measurement. The v1 dashboard shows 94% retention among participants against 81% company-wide; that 13-point gap is almost certainly selection bias, so it is discounted to 3 points here. The CBA sheet reports the case with this stream removed entirely, because it is the softest input in the model. Since a fill is now priced at TA's actual cost rather than an unsourced P350,000 agency fee, this stream carries most of the case: removing it takes the BCR below 1.</t>
         </is>
       </c>
     </row>
@@ -1171,21 +1171,21 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="69" t="inlineStr">
         <is>
           <t>Costed at 1,113 people (the 637-person pilot plus 476 in mass operations) at P61 = US$1. The three-year cost of P2,049,953 is the headline figure and matches the deck.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>The BENEFIT side here counts non-mass participants only, so the base BCR of 3.5 is the CONSERVATIVE case — the deck's "mass-ops benefit excluded" row. The headline BCR of 3.8 adds 54 mass-operations participants at an assumed P260,000 loaded salary; see docs/v2-cba-model.py.</t>
+      <c r="A32" s="69" t="inlineStr">
+        <is>
+          <t>The BENEFIT side here counts non-mass participants only, so the base BCR of 3.8 is the CONSERVATIVE case — the deck's "mass-ops benefit excluded" row. The headline BCR of 4.0 adds 54 mass-operations participants at P15,144.06/month basic; see docs/v2-cba-model.py.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="69" t="inlineStr">
         <is>
           <t>Four of the five run lines are bought in dollars and rise as the peso weakens. The P1,785,500 build is peso labour: it moves with neither the exchange rate nor the population.</t>
         </is>
@@ -1665,11 +1665,11 @@
     <row r="34" ht="15" customHeight="1" s="70">
       <c r="A34" s="81" t="inlineStr">
         <is>
-          <t>Avoided agency fee per internal fill</t>
+          <t>Avoided hiring cost per internal fill</t>
         </is>
       </c>
       <c r="B34" s="89" t="n">
-        <v>350000</v>
+        <v>17095.24</v>
       </c>
       <c r="C34" s="83" t="inlineStr">
         <is>
@@ -1678,18 +1678,18 @@
       </c>
       <c r="D34" s="84" t="inlineStr">
         <is>
-          <t>From the v1 business case.</t>
+          <t>TA cost-per-hire file, 2025, blended on the mix TA actually hired: 186 Band B at P6,977 and 103 Band C at P35,367. Replaces the P350,000 agency fee carried in earlier drafts, which was cited to the v1 business case and does not appear in it.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="70">
       <c r="A35" s="81" t="inlineStr">
         <is>
-          <t>Loaded annual salary, population average</t>
+          <t>Annual basic salary — IT + Operations (non-mass) + HR</t>
         </is>
       </c>
       <c r="B35" s="90" t="n">
-        <v>480000</v>
+        <v>1029634.68</v>
       </c>
       <c r="C35" s="83" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="D35" s="84" t="inlineStr">
         <is>
-          <t>Planning assumption. Validate against payroll.</t>
+          <t>Payroll average monthly basic, September 2026 (P85,802.89) annualised x12. Basic only: the mandatory 13th month and employer contributions are excluded, so the benefit side is stated low. Drives the replacement cost on Benefits.</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="D36" s="84" t="inlineStr">
         <is>
-          <t>Recruitment + ramp + lost output.</t>
+          <t>Recruitment + ramp + lost output, as a share of annual basic.</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D38" s="84" t="inlineStr">
         <is>
-          <t>21 days to fill internally against 58 externally.</t>
+          <t>21 days to fill internally against 58 externally. Costed on the blended Band B/C salary below, not on the non-mass average.</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="D39" s="84" t="inlineStr">
         <is>
-          <t>Non-mass participants only, 19% of the 637. This workbook therefore reproduces the CONSERVATIVE case in the deck — mass-operations retention benefit excluded, BCR 3.5. docs/v2-cba-model.py adds 54 mass-ops participants at a P260,000 loaded salary for the headline BCR 3.8.</t>
+          <t>Non-mass participants only, 19% of the 637. This workbook therefore reproduces the CONSERVATIVE case in the deck — mass-operations retention benefit excluded, BCR 3.8. docs/v2-cba-model.py adds 54 mass-ops participants at P15,144.06/month basic for the headline BCR 4.0.</t>
         </is>
       </c>
     </row>
@@ -1807,10 +1807,30 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="81" t="inlineStr">
+        <is>
+          <t>Annual basic salary — blended Band B / Band C</t>
+        </is>
+      </c>
+      <c r="B42" s="85" t="n">
+        <v>677591.7662283736</v>
+      </c>
+      <c r="C42" s="83" t="inlineStr">
+        <is>
+          <t>₱</t>
+        </is>
+      </c>
+      <c r="D42" s="84" t="inlineStr">
+        <is>
+          <t>Payroll average monthly basic weighted on the 2025 external-hire mix (186 Band B, 103 Band C) = P56,465.98/month, annualised x12. This is the right basis for vacancy days: it is Band B and C roles that internal mobility fills.</t>
+        </is>
+      </c>
+    </row>
     <row r="43" ht="16.5" customHeight="1" s="70">
       <c r="A43" s="73" t="inlineStr">
         <is>
-          <t>SCENARIOS — attributed vacancy hires per year</t>
+          <t>SCENARIOS — attributed internal fills per year</t>
         </is>
       </c>
       <c r="B43" s="74" t="n"/>
@@ -1828,7 +1848,7 @@
       </c>
       <c r="C44" s="83" t="inlineStr">
         <is>
-          <t>hires / year</t>
+          <t>fills / year</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1863,7 @@
       </c>
       <c r="C45" s="83" t="inlineStr">
         <is>
-          <t>hires / year</t>
+          <t>fills / year</t>
         </is>
       </c>
       <c r="D45" s="84" t="inlineStr">
@@ -1863,7 +1883,7 @@
       </c>
       <c r="C46" s="83" t="inlineStr">
         <is>
-          <t>hires / year</t>
+          <t>fills / year</t>
         </is>
       </c>
     </row>
@@ -2978,7 +2998,7 @@
     <row r="2" ht="15" customHeight="1" s="70">
       <c r="A2" s="72" t="inlineStr">
         <is>
-          <t>Two streams. They are not equally defensible — see the provenance column.</t>
+          <t>Two streams. They are not equally defensible — see the provenance column. Salaries are Payroll averages (Sep 2026); cost per hire is TA's 2025 file.</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3028,7 @@
       </c>
       <c r="H5" s="83" t="inlineStr">
         <is>
-          <t>Loaded salary × replacement %</t>
+          <t>Non-mass annual basic × replacement %</t>
         </is>
       </c>
     </row>
@@ -3019,12 +3039,12 @@
         </is>
       </c>
       <c r="B6" s="123">
-        <f>IFERROR(Assumptions!$B$35/Assumptions!$B$37,"n/a")</f>
+        <f>IFERROR(Assumptions!$B$42/Assumptions!$B$37,"n/a")</f>
         <v/>
       </c>
       <c r="H6" s="83" t="inlineStr">
         <is>
-          <t>Loaded salary ÷ working days</t>
+          <t>Blended Band B/C annual basic ÷ working days</t>
         </is>
       </c>
     </row>
@@ -3066,12 +3086,12 @@
       </c>
       <c r="B10" s="98" t="inlineStr">
         <is>
-          <t>Hires/yr</t>
+          <t>Fills/yr</t>
         </is>
       </c>
       <c r="C10" s="98" t="inlineStr">
         <is>
-          <t>Agency fees (₱)</t>
+          <t>Hiring cost avoided (₱)</t>
         </is>
       </c>
       <c r="D10" s="98" t="inlineStr">
@@ -3246,7 +3266,7 @@
     <row r="15" ht="15" customHeight="1" s="70">
       <c r="A15" s="128" t="inlineStr">
         <is>
-          <t>Retention only — zero hires</t>
+          <t>Retention only — zero fills</t>
         </is>
       </c>
       <c r="B15" s="129" t="n">
@@ -3274,7 +3294,7 @@
       </c>
       <c r="H15" s="83" t="inlineStr">
         <is>
-          <t>Stress case: no vacancy hires at all</t>
+          <t>Stress case: no attributed fills at all</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3320,7 @@
       </c>
       <c r="B18" s="84" t="inlineStr">
         <is>
-          <t>Avoided agency fees and vacancy days on permanent roles. Exists ONLY because of the referral tracking — without a confirmed referral the hire is invisible in our data and belongs, as far as anyone can tell, to HC Connect. Requires HC Connect to add a "Growth Marketplace" source value; that commitment does not yet exist.</t>
+          <t>Avoided hiring cost and vacancy days on permanent roles. Exists ONLY because of the referral tracking — without a confirmed referral the hire is invisible in our data and belongs, as far as anyone can tell, to HC Connect. Requires HC Connect to add a "Growth Marketplace" source value; that commitment does not yet exist. At P113,522 a fill this stream is now roughly a fifth of the base-case benefit, so the case no longer stands on it alone.</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3332,7 @@
       </c>
       <c r="B19" s="84" t="inlineStr">
         <is>
-          <t>Retention among gig, DJI and service-offer participants. Needs no attribution, because the marketplace runs those end to end. But the 3-point lift is a discounted judgement, not a measurement — see the stress rows above and the Legend sheet.</t>
+          <t>Retention among gig, DJI and service-offer participants. Needs no attribution, because the marketplace runs those end to end. It now carries most of the case, and the 3-point lift is still a discounted judgement rather than a measurement — which is why the year-one holdout is the gating instrument, not a nicety. See the stress rows above.</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6697,7 @@
     <row r="6" ht="15" customHeight="1" s="70">
       <c r="A6" s="81" t="inlineStr">
         <is>
-          <t>Conservative — 2 hires/yr</t>
+          <t>Conservative — 2 fills/yr</t>
         </is>
       </c>
       <c r="B6" s="102">
@@ -6720,7 +6740,7 @@
     <row r="7" ht="15" customHeight="1" s="70">
       <c r="A7" s="108" t="inlineStr">
         <is>
-          <t>Base — 4 hires/yr</t>
+          <t>Base — 4 fills/yr</t>
         </is>
       </c>
       <c r="B7" s="126">
@@ -6763,7 +6783,7 @@
     <row r="8" ht="15" customHeight="1" s="70">
       <c r="A8" s="81" t="inlineStr">
         <is>
-          <t>Optimistic — 7 hires/yr</t>
+          <t>Optimistic — 7 fills/yr</t>
         </is>
       </c>
       <c r="B8" s="102">
@@ -6849,7 +6869,7 @@
     <row r="10" ht="15" customHeight="1" s="70">
       <c r="A10" s="128" t="inlineStr">
         <is>
-          <t>Retention only, zero hires</t>
+          <t>Retention only, zero fills</t>
         </is>
       </c>
       <c r="B10" s="102">
@@ -6908,7 +6928,7 @@
     <row r="13" ht="33.75" customHeight="1" s="70">
       <c r="A13" s="76" t="inlineStr">
         <is>
-          <t>The case survives the removal of either benefit stream. Strip retention out — the softest input in the model — and the ratio holds well above 1. Strip out every vacancy hire instead, and retention alone still repays the cost inside the horizon. Both halves would have to be wrong at the same time for this to fail.</t>
+          <t>Read the retention-excluded row before quoting the base case. Pricing a fill at what TA actually spends — P113,522, not the old P350,000 — moves the weight of this case onto retention, which is roughly six-sevenths of the base-case benefit. Remove mass operations, refuse the vacancy-day credit, or lose attribution entirely and the ratio still clears 3. Remove retention and it does not. That is the one measurement worth designing properly before the build starts.</t>
         </is>
       </c>
     </row>
@@ -6945,7 +6965,7 @@
     <row r="17" ht="30" customHeight="1" s="70">
       <c r="A17" s="81" t="inlineStr">
         <is>
-          <t>Attributed hires per year to break even</t>
+          <t>Attributed fills per year to break even</t>
         </is>
       </c>
       <c r="B17" s="119">
@@ -6954,7 +6974,7 @@
       </c>
       <c r="D17" s="84" t="inlineStr">
         <is>
-          <t>Three-year cost ÷ (ramped years × value per attributed hire). Retention excluded entirely — this is the hires-only bar.</t>
+          <t>Three-year cost ÷ (ramped years × value per attributed fill, P113,522). Retention excluded entirely — this is the fills-only bar.</t>
         </is>
       </c>
     </row>
@@ -6981,7 +7001,7 @@
       </c>
       <c r="D19" s="83" t="inlineStr">
         <is>
-          <t>Three-year cost ÷ annual retention benefit. Assumes zero attributed vacancy hires.</t>
+          <t>Three-year cost ÷ annual retention benefit. Assumes zero attributed fills.</t>
         </is>
       </c>
     </row>
@@ -7244,14 +7264,14 @@
       </c>
       <c r="D16" s="84" t="inlineStr">
         <is>
-          <t>The softest input removed entirely. The case still clears comfortably.</t>
+          <t>The softest input removed entirely. At the corrected P113,522 per fill this is where the case fails — the reason the retention holdout is now a gate.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="70">
       <c r="A17" s="81" t="inlineStr">
         <is>
-          <t>No attributed hires at all</t>
+          <t>No attributed fills at all</t>
         </is>
       </c>
       <c r="B17" s="102">
@@ -7291,11 +7311,11 @@
     <row r="19" ht="30" customHeight="1" s="70">
       <c r="A19" s="81" t="inlineStr">
         <is>
-          <t>Agency fee is ₱250,000, not ₱350,000</t>
+          <t>Hiring cost avoided only — no vacancy-day credit</t>
         </is>
       </c>
       <c r="B19" s="102">
-        <f>(Benefits!$B$12*250000+Benefits!$D$12+Benefits!$B$7)*(2+Assumptions!$B$41)</f>
+        <f>(Benefits!$B$12*Assumptions!$B$34+Benefits!$B$7)*(2+Assumptions!$B$41)</f>
         <v/>
       </c>
       <c r="C19" s="120">
@@ -7304,14 +7324,14 @@
       </c>
       <c r="D19" s="84" t="inlineStr">
         <is>
-          <t>Validate the avoided-fee assumption with recruitment.</t>
+          <t>Treats the 37 vacancy days as unrecoverable. The harder floor on the attributed stream.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="51.75" customHeight="1" s="70">
       <c r="A21" s="140" t="inlineStr">
         <is>
-          <t>The two that actually decide this: whether HC Connect adds the source field (without it only the owned stream is defensible), and whether the retention lift is real (it is a judgement here, and a holdout is the only way to settle it — promote a random half of open requisitions for a quarter and compare).</t>
+          <t>The two that actually decide this: whether the retention lift is real (it is a judgement here, and a holdout is the only way to settle it — promote a random half of open requisitions for a quarter and compare), and whether HC Connect adds the source field (without it only the owned stream is defensible).</t>
         </is>
       </c>
     </row>
